--- a/TC Finishing D^t Solution Migration_2026.xlsx
+++ b/TC Finishing D^t Solution Migration_2026.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corningonline-my.sharepoint.com/personal/wangm44_corning_com/Documents/桌面/Project/Dt_Quality_Roadmap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="14_{89C73AE1-523B-4B10-8D61-849337C2FCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4361CD7-4211-495E-B2CC-F5D28CC65FEB}"/>
+  <xr:revisionPtr revIDLastSave="515" documentId="14_{89C73AE1-523B-4B10-8D61-849337C2FCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1BB2A86-7869-4B1B-95BD-A204095BBA20}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Definition" sheetId="6" r:id="rId1"/>
-    <sheet name="System" sheetId="2" r:id="rId2"/>
-    <sheet name="Melting" sheetId="9" r:id="rId3"/>
-    <sheet name="Finishing" sheetId="5" r:id="rId4"/>
-    <sheet name="Finishing_TC_Summary" sheetId="8" r:id="rId5"/>
-    <sheet name="Finishing_TC_Item" sheetId="7" r:id="rId6"/>
+    <sheet name="工作表1" sheetId="10" r:id="rId2"/>
+    <sheet name="System" sheetId="2" r:id="rId3"/>
+    <sheet name="Melting" sheetId="9" r:id="rId4"/>
+    <sheet name="Finishing" sheetId="5" r:id="rId5"/>
+    <sheet name="Finishing_TC_Summary" sheetId="8" r:id="rId6"/>
+    <sheet name="Finishing_TC_Item" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Finishing_TC_Summary!$E$3:$E$28</definedName>
-    <definedName name="ExternalData_1" localSheetId="3" hidden="1">Finishing!$A$1:$BK$48</definedName>
-    <definedName name="ExternalData_1" localSheetId="1" hidden="1">System!$A$1:$BP$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Finishing_TC_Summary!$E$3:$E$28</definedName>
+    <definedName name="ExternalData_1" localSheetId="4" hidden="1">Finishing!$A$1:$BK$48</definedName>
+    <definedName name="ExternalData_1" localSheetId="2" hidden="1">System!$A$1:$BP$6</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -166,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5106" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5524" uniqueCount="482">
   <si>
     <t>Status</t>
   </si>
@@ -484,9 +485,6 @@
     <t>BDS</t>
   </si>
   <si>
-    <t>LCVS</t>
-  </si>
-  <si>
     <t>MMA detection system</t>
   </si>
   <si>
@@ -551,9 +549,6 @@
   </si>
   <si>
     <t xml:space="preserve">FS BKG sensor </t>
-  </si>
-  <si>
-    <t>Pre Washer</t>
   </si>
   <si>
     <t>EDS ( Edge Detection System)</t>
@@ -1174,25 +1169,10 @@
     <t>ARWC+auto drop</t>
   </si>
   <si>
-    <t>BOD cold end breakage detection</t>
-  </si>
-  <si>
-    <t>RFCD</t>
-  </si>
-  <si>
     <t>BTF</t>
   </si>
   <si>
-    <t>BKG detection</t>
-  </si>
-  <si>
     <t>CFMS</t>
-  </si>
-  <si>
-    <t>CFMS scoring quality analysis system</t>
-  </si>
-  <si>
-    <t>CFMS2 scoring quality analysis system</t>
   </si>
   <si>
     <t>FB</t>
@@ -1216,9 +1196,6 @@
     <t>OCDS</t>
   </si>
   <si>
-    <t>LAM</t>
-  </si>
-  <si>
     <t>LAM 3-axis Sync. Diagnosis</t>
   </si>
   <si>
@@ -1230,98 +1207,704 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>OHCV</t>
+  </si>
+  <si>
+    <t>ST10</t>
+  </si>
+  <si>
+    <t>TAM</t>
+  </si>
+  <si>
+    <t>Auto Scoring Pressure Compensation</t>
+  </si>
+  <si>
+    <t>TAM FS position detection</t>
+  </si>
+  <si>
+    <t>TAM Score Health Diagnosis</t>
+  </si>
+  <si>
+    <t>TAM median depth auto control</t>
+  </si>
+  <si>
+    <t>VBS</t>
+  </si>
+  <si>
+    <t>Advance Sheet Guide Solution</t>
+  </si>
+  <si>
+    <t>non-QA SC preventive BSG</t>
+  </si>
+  <si>
+    <t>Swing sensor in VBS entrance</t>
+  </si>
+  <si>
+    <t>Forming</t>
+  </si>
+  <si>
+    <t>FDM</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>Attribute and process AI platform</t>
+  </si>
+  <si>
+    <t>Auto detection of FDM Catcher Drip</t>
+  </si>
+  <si>
+    <t>Auto detection of FDM ER gob stream</t>
+  </si>
+  <si>
+    <t>DDS</t>
+  </si>
+  <si>
+    <t>FDM RRS edge fitting</t>
+  </si>
+  <si>
+    <t>LC TAM IR</t>
+  </si>
+  <si>
+    <t>P3CDS</t>
+  </si>
+  <si>
+    <t>RRS SSD</t>
+  </si>
+  <si>
+    <t>Smart packoff for forming attibute abnomy detection</t>
+  </si>
+  <si>
+    <t>aDFC+MIRUS</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>fill door &amp; Stack image analysis</t>
+  </si>
+  <si>
+    <t>Melting</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Process</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Process</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Station</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FDM</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forming</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOD</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAM</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>VBS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inspection</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CBW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ST10</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cutting</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre Washer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ULB</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Film peeling</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AVM</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CC</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BJ</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>USN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DB</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RB</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cutting</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ISIS/LSIS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MRS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>OGA</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>OHCV/TRCV</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>INSP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Washer</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Beveling</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inclusion AI platform</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inclusion AI platform</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LAM</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LAM</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Auto Scoring Pressure Compensation</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFMS scoring quality analysis system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Advance Sheet Guide Solution</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFMS scoring quality analysis system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFMS2 scoring quality analysis system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFMS2 scoring quality analysis system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>crBIS Detection Enhancement (Drip)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>OCDS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LAM 3-axis Sync. Diagnosis</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LAM BKG/Crack detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>LBD 裂必擋 (Laminating Breakage Detection)</t>
-  </si>
-  <si>
-    <t>OHCV</t>
-  </si>
-  <si>
-    <t>ST10</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Laminating Breakage Detection</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Online Condensate Detection System</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cutting Face Measurement System</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>edge defect detection system</t>
-  </si>
-  <si>
-    <t>TAM</t>
-  </si>
-  <si>
-    <t>Auto Scoring Pressure Compensation</t>
-  </si>
-  <si>
-    <t>TAM FS position detection</t>
-  </si>
-  <si>
-    <t>TAM Score Health Diagnosis</t>
-  </si>
-  <si>
-    <t>TAM median depth auto control</t>
-  </si>
-  <si>
-    <t>VBS</t>
-  </si>
-  <si>
-    <t>Advance Sheet Guide Solution</t>
-  </si>
-  <si>
-    <t>non-QA SC preventive BSG</t>
-  </si>
-  <si>
-    <t>Swing sensor in VBS entrance</t>
-  </si>
-  <si>
-    <t>Forming</t>
-  </si>
-  <si>
-    <t>FDM</t>
-  </si>
-  <si>
-    <t>ADP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>edge defect detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paper folding detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BTF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BKG detection</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BKG detection</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFS MMA collapsed auto recovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cut size auto adjustment</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cutting MC auto measurement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cutting MC auto measurement</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cutting SQ auto adjustment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cutting SQ auto adjustment</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EDS ( Edge Detection System)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FS BKG detection system</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FS BKG detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FS BKG sensor </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FS BKG sensor </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCVS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glass shift detection - LCVS (Low cost vision system)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Auto-grinding amount adjustment</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAM sensor</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SA/Tilt</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IPC/FPC fixed pattern detection thru. D^t</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paper feeder</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Paper transporter</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glass floating height detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Linearity variation control system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LVCS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BDS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EDS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vibration Prediction &amp; Measurement System</t>
+  </si>
+  <si>
+    <t>VPMS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Container BKG Detection System</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CBDS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Foreign Material Detection System</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FMDS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCVS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low cost vision system; Glass shift detection</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>sPD data foundation</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>System</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FG quality management system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drive unit alignment real time monitor</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vacuum pad push amount detection and auto compensation</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rubicon reduction system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ARWC+auto drop</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Attribute and process AI platform</t>
-  </si>
-  <si>
-    <t>Auto detection of FDM Catcher Drip</t>
-  </si>
-  <si>
-    <t>Auto detection of FDM ER gob stream</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ARWC+auto drop</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Auto Roll Wearing Compensation</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DDS</t>
-  </si>
-  <si>
-    <t>FDM RRS edge fitting</t>
-  </si>
-  <si>
-    <t>LC TAM IR</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>P3 Crack out detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>P3CDS</t>
-  </si>
-  <si>
-    <t>RRS SSD</t>
-  </si>
-  <si>
-    <t>Smart packoff for forming attibute abnomy detection</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drip detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>aDFC+MIRUS</t>
-  </si>
-  <si>
-    <t>Inclusion AI platform</t>
-  </si>
-  <si>
-    <t>PM</t>
-  </si>
-  <si>
-    <t>fill door &amp; Stack image analysis</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RRS sheet shape detection</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">OHCV carrier online alignment detection system </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CBW MMA detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Packing quality detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RFCD</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IR laser (MIRUS) to control ribbon thickness</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quality Attribute</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RFCD</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOD cold end breakage detection</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crack</t>
+  </si>
+  <si>
+    <t>TAM Breakage Visualization System</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TBVS</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rubicon / MSL</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BKG / Crack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FSW / MRV</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BKG / ADG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MC / BKG / ADG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FB</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EG / CG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scratch / Crack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheet length</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thickness / OD</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inclusion / BKG / Crack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rubicon / Crack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Devit</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drip</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inclusion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MRV</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scratch</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BKG / scratch / Crack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vaccum online system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Edge quality/ BKG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Edge Detection System; BKG detection system; ULB BKG detection system</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Edge quality / BKG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Edge quality</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BKG / Scratch / Crack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BKG / Scratch</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fix Pattern / OK defect density</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Glass shift / Paper overhang</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mura</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>PD</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Fix Pattern</t>
+  </si>
+  <si>
+    <t>Pitch defect</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFS belt detection</t>
+  </si>
+  <si>
+    <t>Auto overlap adjustment</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cell grind process automation</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BKG detection system; Wet zone glass BKG detective system; Cell grinder BKG detection system at OUT C/V</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1440,6 +2023,15 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1899,7 +2491,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2078,6 +2670,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2527,13 +3120,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2F3485B2-DE5B-495C-815F-2A49A3B81D3C}" name="Table1__2" displayName="Table1__2" ref="A1:AU36" totalsRowShown="0">
-  <autoFilter ref="A1:AU36" xr:uid="{3512359C-E6FA-461A-820A-DB88FDBC29B7}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="BOD"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AU36" xr:uid="{3512359C-E6FA-461A-820A-DB88FDBC29B7}"/>
   <tableColumns count="47">
     <tableColumn id="1" xr3:uid="{9749C07D-341F-477B-9D22-002314C560CB}" name="Process category" dataDxfId="46"/>
     <tableColumn id="2" xr3:uid="{7AD7D549-A4AF-412E-A835-5A1655D3E91A}" name="Process" dataDxfId="45"/>
@@ -3012,7 +3599,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>13</v>
@@ -3033,6 +3620,1444 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CA36034-F39F-425C-A05E-866490AA24FD}">
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" customWidth="1"/>
+    <col min="6" max="6" width="101.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="64" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="64" t="s">
+        <v>440</v>
+      </c>
+      <c r="F1" s="64" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E3" t="s">
+        <v>457</v>
+      </c>
+      <c r="F3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E4" t="s">
+        <v>454</v>
+      </c>
+      <c r="F4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D5" t="s">
+        <v>315</v>
+      </c>
+      <c r="E5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E7" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" t="s">
+        <v>429</v>
+      </c>
+      <c r="E8" t="s">
+        <v>443</v>
+      </c>
+      <c r="F8" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C10" t="s">
+        <v>313</v>
+      </c>
+      <c r="D10" t="s">
+        <v>320</v>
+      </c>
+      <c r="E10" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C11" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" t="s">
+        <v>431</v>
+      </c>
+      <c r="E11" t="s">
+        <v>443</v>
+      </c>
+      <c r="F11" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>287</v>
+      </c>
+      <c r="B12" t="s">
+        <v>332</v>
+      </c>
+      <c r="C12" t="s">
+        <v>313</v>
+      </c>
+      <c r="D12" t="s">
+        <v>322</v>
+      </c>
+      <c r="E12" t="s">
+        <v>448</v>
+      </c>
+      <c r="F12" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" t="s">
+        <v>332</v>
+      </c>
+      <c r="C13" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E13" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C14" t="s">
+        <v>313</v>
+      </c>
+      <c r="D14" t="s">
+        <v>433</v>
+      </c>
+      <c r="E14" t="s">
+        <v>455</v>
+      </c>
+      <c r="F14" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>287</v>
+      </c>
+      <c r="B15" t="s">
+        <v>333</v>
+      </c>
+      <c r="C15" t="s">
+        <v>334</v>
+      </c>
+      <c r="D15" t="s">
+        <v>304</v>
+      </c>
+      <c r="E15" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>287</v>
+      </c>
+      <c r="B16" t="s">
+        <v>333</v>
+      </c>
+      <c r="C16" t="s">
+        <v>334</v>
+      </c>
+      <c r="D16" t="s">
+        <v>445</v>
+      </c>
+      <c r="E16" t="s">
+        <v>446</v>
+      </c>
+      <c r="F16" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>287</v>
+      </c>
+      <c r="B17" t="s">
+        <v>333</v>
+      </c>
+      <c r="C17" t="s">
+        <v>334</v>
+      </c>
+      <c r="D17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E17" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>287</v>
+      </c>
+      <c r="B18" t="s">
+        <v>333</v>
+      </c>
+      <c r="C18" t="s">
+        <v>334</v>
+      </c>
+      <c r="D18" t="s">
+        <v>306</v>
+      </c>
+      <c r="E18" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B19" t="s">
+        <v>333</v>
+      </c>
+      <c r="C19" t="s">
+        <v>334</v>
+      </c>
+      <c r="D19" t="s">
+        <v>307</v>
+      </c>
+      <c r="E19" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>287</v>
+      </c>
+      <c r="B20" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" t="s">
+        <v>334</v>
+      </c>
+      <c r="D20" t="s">
+        <v>441</v>
+      </c>
+      <c r="E20" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>287</v>
+      </c>
+      <c r="B21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C21" t="s">
+        <v>335</v>
+      </c>
+      <c r="D21" t="s">
+        <v>309</v>
+      </c>
+      <c r="E21" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>287</v>
+      </c>
+      <c r="B22" t="s">
+        <v>333</v>
+      </c>
+      <c r="C22" t="s">
+        <v>335</v>
+      </c>
+      <c r="D22" t="s">
+        <v>310</v>
+      </c>
+      <c r="E22" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>287</v>
+      </c>
+      <c r="B23" t="s">
+        <v>333</v>
+      </c>
+      <c r="C23" t="s">
+        <v>335</v>
+      </c>
+      <c r="D23" t="s">
+        <v>311</v>
+      </c>
+      <c r="E23" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>287</v>
+      </c>
+      <c r="B24" t="s">
+        <v>333</v>
+      </c>
+      <c r="C24" t="s">
+        <v>336</v>
+      </c>
+      <c r="D24" t="s">
+        <v>369</v>
+      </c>
+      <c r="E24" t="s">
+        <v>450</v>
+      </c>
+      <c r="F24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>287</v>
+      </c>
+      <c r="B25" t="s">
+        <v>333</v>
+      </c>
+      <c r="C25" t="s">
+        <v>336</v>
+      </c>
+      <c r="D25" t="s">
+        <v>371</v>
+      </c>
+      <c r="E25" t="s">
+        <v>450</v>
+      </c>
+      <c r="F25" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>287</v>
+      </c>
+      <c r="B26" t="s">
+        <v>333</v>
+      </c>
+      <c r="C26" t="s">
+        <v>336</v>
+      </c>
+      <c r="D26" t="s">
+        <v>372</v>
+      </c>
+      <c r="E26" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>287</v>
+      </c>
+      <c r="B27" t="s">
+        <v>333</v>
+      </c>
+      <c r="C27" t="s">
+        <v>336</v>
+      </c>
+      <c r="D27" t="s">
+        <v>297</v>
+      </c>
+      <c r="E27" t="s">
+        <v>469</v>
+      </c>
+      <c r="F27" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>287</v>
+      </c>
+      <c r="B28" t="s">
+        <v>333</v>
+      </c>
+      <c r="C28" t="s">
+        <v>365</v>
+      </c>
+      <c r="D28" t="s">
+        <v>298</v>
+      </c>
+      <c r="E28" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>287</v>
+      </c>
+      <c r="B29" t="s">
+        <v>333</v>
+      </c>
+      <c r="C29" t="s">
+        <v>365</v>
+      </c>
+      <c r="D29" t="s">
+        <v>377</v>
+      </c>
+      <c r="E29" t="s">
+        <v>449</v>
+      </c>
+      <c r="F29" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>287</v>
+      </c>
+      <c r="B30" t="s">
+        <v>333</v>
+      </c>
+      <c r="C30" t="s">
+        <v>302</v>
+      </c>
+      <c r="D30" t="s">
+        <v>381</v>
+      </c>
+      <c r="E30" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>287</v>
+      </c>
+      <c r="B31" t="s">
+        <v>333</v>
+      </c>
+      <c r="C31" t="s">
+        <v>451</v>
+      </c>
+      <c r="D31" t="s">
+        <v>187</v>
+      </c>
+      <c r="E31" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>287</v>
+      </c>
+      <c r="B32" t="s">
+        <v>333</v>
+      </c>
+      <c r="C32" t="s">
+        <v>383</v>
+      </c>
+      <c r="D32" t="s">
+        <v>385</v>
+      </c>
+      <c r="E32" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
+        <v>354</v>
+      </c>
+      <c r="C33" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" t="s">
+        <v>354</v>
+      </c>
+      <c r="C34" t="s">
+        <v>339</v>
+      </c>
+      <c r="D34" t="s">
+        <v>386</v>
+      </c>
+      <c r="E34" t="s">
+        <v>205</v>
+      </c>
+      <c r="F34" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" t="s">
+        <v>354</v>
+      </c>
+      <c r="C35" t="s">
+        <v>339</v>
+      </c>
+      <c r="D35" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" t="s">
+        <v>354</v>
+      </c>
+      <c r="C36" t="s">
+        <v>354</v>
+      </c>
+      <c r="D36" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s">
+        <v>354</v>
+      </c>
+      <c r="C37" t="s">
+        <v>354</v>
+      </c>
+      <c r="D37" t="s">
+        <v>464</v>
+      </c>
+      <c r="E37" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" t="s">
+        <v>354</v>
+      </c>
+      <c r="D38" t="s">
+        <v>387</v>
+      </c>
+      <c r="E38" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" t="s">
+        <v>354</v>
+      </c>
+      <c r="C39" t="s">
+        <v>354</v>
+      </c>
+      <c r="D39" t="s">
+        <v>389</v>
+      </c>
+      <c r="E39" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" t="s">
+        <v>354</v>
+      </c>
+      <c r="C40" t="s">
+        <v>354</v>
+      </c>
+      <c r="D40" t="s">
+        <v>391</v>
+      </c>
+      <c r="E40" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" t="s">
+        <v>354</v>
+      </c>
+      <c r="C41" t="s">
+        <v>354</v>
+      </c>
+      <c r="D41" t="s">
+        <v>396</v>
+      </c>
+      <c r="E41" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" t="s">
+        <v>354</v>
+      </c>
+      <c r="C42" t="s">
+        <v>354</v>
+      </c>
+      <c r="D42" t="s">
+        <v>394</v>
+      </c>
+      <c r="E42" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" t="s">
+        <v>354</v>
+      </c>
+      <c r="C43" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" t="s">
+        <v>354</v>
+      </c>
+      <c r="C44" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" t="s">
+        <v>361</v>
+      </c>
+      <c r="C45" t="s">
+        <v>348</v>
+      </c>
+      <c r="D45" t="s">
+        <v>408</v>
+      </c>
+      <c r="E45" t="s">
+        <v>205</v>
+      </c>
+      <c r="F45" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>361</v>
+      </c>
+      <c r="C46" t="s">
+        <v>348</v>
+      </c>
+      <c r="D46" t="s">
+        <v>417</v>
+      </c>
+      <c r="E46" t="s">
+        <v>219</v>
+      </c>
+      <c r="F46" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>361</v>
+      </c>
+      <c r="C47" t="s">
+        <v>346</v>
+      </c>
+      <c r="D47" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" t="s">
+        <v>361</v>
+      </c>
+      <c r="C48" t="s">
+        <v>346</v>
+      </c>
+      <c r="D48" t="s">
+        <v>399</v>
+      </c>
+      <c r="E48" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" t="s">
+        <v>361</v>
+      </c>
+      <c r="C49" t="s">
+        <v>347</v>
+      </c>
+      <c r="D49" t="s">
+        <v>409</v>
+      </c>
+      <c r="E49" t="s">
+        <v>219</v>
+      </c>
+      <c r="F49" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" t="s">
+        <v>360</v>
+      </c>
+      <c r="C50" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" t="s">
+        <v>360</v>
+      </c>
+      <c r="C51" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" t="s">
+        <v>360</v>
+      </c>
+      <c r="C52" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" t="s">
+        <v>360</v>
+      </c>
+      <c r="C53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" t="s">
+        <v>360</v>
+      </c>
+      <c r="C54" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" t="s">
+        <v>360</v>
+      </c>
+      <c r="C55" t="s">
+        <v>343</v>
+      </c>
+      <c r="D55" t="s">
+        <v>410</v>
+      </c>
+      <c r="E55" t="s">
+        <v>447</v>
+      </c>
+      <c r="F55" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" t="s">
+        <v>359</v>
+      </c>
+      <c r="C56" t="s">
+        <v>401</v>
+      </c>
+      <c r="D56" t="s">
+        <v>400</v>
+      </c>
+      <c r="E56" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" t="s">
+        <v>359</v>
+      </c>
+      <c r="C57" t="s">
+        <v>401</v>
+      </c>
+      <c r="D57" t="s">
+        <v>422</v>
+      </c>
+      <c r="E57" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>99</v>
+      </c>
+      <c r="B58" t="s">
+        <v>359</v>
+      </c>
+      <c r="C58" t="s">
+        <v>176</v>
+      </c>
+      <c r="D58" t="s">
+        <v>402</v>
+      </c>
+      <c r="E58" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" t="s">
+        <v>359</v>
+      </c>
+      <c r="C59" t="s">
+        <v>178</v>
+      </c>
+      <c r="D59" t="s">
+        <v>175</v>
+      </c>
+      <c r="E59" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" t="s">
+        <v>359</v>
+      </c>
+      <c r="C60" t="s">
+        <v>355</v>
+      </c>
+      <c r="D60" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61" t="s">
+        <v>359</v>
+      </c>
+      <c r="C61" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>99</v>
+      </c>
+      <c r="B62" t="s">
+        <v>359</v>
+      </c>
+      <c r="C62" t="s">
+        <v>181</v>
+      </c>
+      <c r="D62" t="s">
+        <v>405</v>
+      </c>
+      <c r="E62" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>99</v>
+      </c>
+      <c r="B63" t="s">
+        <v>359</v>
+      </c>
+      <c r="C63" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" t="s">
+        <v>359</v>
+      </c>
+      <c r="C64" t="s">
+        <v>420</v>
+      </c>
+      <c r="D64" t="s">
+        <v>421</v>
+      </c>
+      <c r="E64" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>99</v>
+      </c>
+      <c r="B65" t="s">
+        <v>180</v>
+      </c>
+      <c r="C65" t="s">
+        <v>181</v>
+      </c>
+      <c r="D65" t="s">
+        <v>182</v>
+      </c>
+      <c r="E65" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" t="s">
+        <v>180</v>
+      </c>
+      <c r="C66" t="s">
+        <v>183</v>
+      </c>
+      <c r="D66" t="s">
+        <v>412</v>
+      </c>
+      <c r="E66" t="s">
+        <v>470</v>
+      </c>
+      <c r="F66" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" t="s">
+        <v>180</v>
+      </c>
+      <c r="C67" t="s">
+        <v>358</v>
+      </c>
+      <c r="D67" t="s">
+        <v>412</v>
+      </c>
+      <c r="E67" t="s">
+        <v>470</v>
+      </c>
+      <c r="F67" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" t="s">
+        <v>180</v>
+      </c>
+      <c r="C68" t="s">
+        <v>358</v>
+      </c>
+      <c r="D68" t="s">
+        <v>435</v>
+      </c>
+      <c r="E68" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>99</v>
+      </c>
+      <c r="B69" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" t="s">
+        <v>185</v>
+      </c>
+      <c r="D69" t="s">
+        <v>414</v>
+      </c>
+      <c r="E69" t="s">
+        <v>205</v>
+      </c>
+      <c r="F69" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" t="s">
+        <v>180</v>
+      </c>
+      <c r="C70" t="s">
+        <v>185</v>
+      </c>
+      <c r="D70" t="s">
+        <v>187</v>
+      </c>
+      <c r="E70" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>99</v>
+      </c>
+      <c r="B71" t="s">
+        <v>180</v>
+      </c>
+      <c r="C71" t="s">
+        <v>185</v>
+      </c>
+      <c r="D71" t="s">
+        <v>437</v>
+      </c>
+      <c r="E71" t="s">
+        <v>205</v>
+      </c>
+      <c r="F71" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" t="s">
+        <v>180</v>
+      </c>
+      <c r="C72" t="s">
+        <v>185</v>
+      </c>
+      <c r="D72" t="s">
+        <v>416</v>
+      </c>
+      <c r="E72" t="s">
+        <v>205</v>
+      </c>
+      <c r="F72" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>99</v>
+      </c>
+      <c r="B73" t="s">
+        <v>180</v>
+      </c>
+      <c r="C73" t="s">
+        <v>185</v>
+      </c>
+      <c r="D73" t="s">
+        <v>189</v>
+      </c>
+      <c r="E73" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" t="s">
+        <v>180</v>
+      </c>
+      <c r="C74" t="s">
+        <v>185</v>
+      </c>
+      <c r="D74" t="s">
+        <v>423</v>
+      </c>
+      <c r="E74" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>99</v>
+      </c>
+      <c r="B75" t="s">
+        <v>180</v>
+      </c>
+      <c r="C75" t="s">
+        <v>403</v>
+      </c>
+      <c r="D75" t="s">
+        <v>412</v>
+      </c>
+      <c r="E75" t="s">
+        <v>205</v>
+      </c>
+      <c r="F75" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" t="s">
+        <v>180</v>
+      </c>
+      <c r="C76" t="s">
+        <v>404</v>
+      </c>
+      <c r="D76" t="s">
+        <v>412</v>
+      </c>
+      <c r="E76" t="s">
+        <v>205</v>
+      </c>
+      <c r="F76" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>420</v>
+      </c>
+      <c r="B77" t="s">
+        <v>420</v>
+      </c>
+      <c r="C77" t="s">
+        <v>420</v>
+      </c>
+      <c r="D77" t="s">
+        <v>226</v>
+      </c>
+      <c r="E77" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>420</v>
+      </c>
+      <c r="B78" t="s">
+        <v>420</v>
+      </c>
+      <c r="C78" t="s">
+        <v>420</v>
+      </c>
+      <c r="D78" t="s">
+        <v>85</v>
+      </c>
+      <c r="E78" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>420</v>
+      </c>
+      <c r="B79" t="s">
+        <v>420</v>
+      </c>
+      <c r="C79" t="s">
+        <v>420</v>
+      </c>
+      <c r="D79" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>420</v>
+      </c>
+      <c r="B80" t="s">
+        <v>420</v>
+      </c>
+      <c r="C80" t="s">
+        <v>420</v>
+      </c>
+      <c r="D80" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>420</v>
+      </c>
+      <c r="B81" t="s">
+        <v>420</v>
+      </c>
+      <c r="C81" t="s">
+        <v>420</v>
+      </c>
+      <c r="D81" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>420</v>
+      </c>
+      <c r="B82" t="s">
+        <v>420</v>
+      </c>
+      <c r="C82" t="s">
+        <v>420</v>
+      </c>
+      <c r="D82" t="s">
+        <v>419</v>
+      </c>
+      <c r="E82" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>420</v>
+      </c>
+      <c r="B83" t="s">
+        <v>420</v>
+      </c>
+      <c r="C83" t="s">
+        <v>420</v>
+      </c>
+      <c r="D83" t="s">
+        <v>171</v>
+      </c>
+      <c r="E83" t="s">
+        <v>474</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051C37CA-A1A2-460A-93E4-CB816C1343E6}">
   <dimension ref="A1:BP6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -4229,7 +6254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C28F886-A301-4DD7-AF15-432336C9DB13}">
   <dimension ref="A1:AU39"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -4262,10 +6287,10 @@
         <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>328</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>330</v>
       </c>
       <c r="D1" t="s">
         <v>19</v>
@@ -4277,141 +6302,141 @@
         <v>80</v>
       </c>
       <c r="G1" t="s">
+        <v>249</v>
+      </c>
+      <c r="H1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I1" t="s">
         <v>251</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>252</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>253</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>254</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>255</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>256</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>257</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>258</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>259</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>260</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>261</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>262</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>263</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>264</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>265</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>266</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>267</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>268</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>269</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>270</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>271</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>272</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>273</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>274</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>275</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>276</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>277</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>278</v>
       </c>
       <c r="AI1" t="s">
         <v>81</v>
       </c>
       <c r="AJ1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AK1" t="s">
         <v>82</v>
       </c>
       <c r="AL1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AM1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AN1" t="s">
         <v>83</v>
       </c>
       <c r="AO1" t="s">
+        <v>280</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>281</v>
+      </c>
+      <c r="AQ1" t="s">
         <v>282</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>284</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>285</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>286</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>287</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D2" t="s">
-        <v>291</v>
+        <v>427</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
@@ -4545,16 +6570,16 @@
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="B3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D3" t="s">
-        <v>292</v>
+        <v>442</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4688,16 +6713,16 @@
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D4" t="s">
-        <v>293</v>
+        <v>438</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
@@ -4831,16 +6856,16 @@
     </row>
     <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
         <v>290</v>
       </c>
-      <c r="C5" t="s">
-        <v>294</v>
-      </c>
       <c r="D5" t="s">
-        <v>295</v>
+        <v>384</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4974,16 +6999,16 @@
     </row>
     <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C6" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D6" t="s">
-        <v>297</v>
+        <v>367</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -5117,16 +7142,16 @@
     </row>
     <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C7" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D7" t="s">
-        <v>298</v>
+        <v>370</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -5260,16 +7285,16 @@
     </row>
     <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D8" t="s">
-        <v>222</v>
+        <v>382</v>
       </c>
       <c r="E8" t="s">
         <v>4</v>
@@ -5403,30 +7428,30 @@
     </row>
     <row r="9" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D10" t="s">
-        <v>304</v>
+        <v>373</v>
       </c>
       <c r="E10" t="s">
         <v>2</v>
@@ -5560,16 +7585,16 @@
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C11" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="D11" t="s">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -5703,16 +7728,16 @@
     </row>
     <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C12" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D12" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -5846,30 +7871,30 @@
     </row>
     <row r="13" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>309</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B14" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C14" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D14" t="s">
-        <v>304</v>
+        <v>373</v>
       </c>
       <c r="E14" t="s">
         <v>2</v>
@@ -6003,16 +8028,16 @@
     </row>
     <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B15" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C15" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="D15" t="s">
-        <v>312</v>
+        <v>380</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -6146,16 +8171,16 @@
     </row>
     <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B16" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C16" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D16" t="s">
-        <v>314</v>
+        <v>366</v>
       </c>
       <c r="E16" t="s">
         <v>2</v>
@@ -6289,16 +8314,16 @@
     </row>
     <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D17" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E17" t="s">
         <v>2</v>
@@ -6432,16 +8457,16 @@
     </row>
     <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B18" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C18" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D18" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -6575,16 +8600,16 @@
     </row>
     <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C19" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D19" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="E19" t="s">
         <v>14</v>
@@ -6718,16 +8743,16 @@
     </row>
     <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D20" t="s">
-        <v>319</v>
+        <v>368</v>
       </c>
       <c r="E20" t="s">
         <v>2</v>
@@ -6861,16 +8886,16 @@
     </row>
     <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C21" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D21" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="E21" t="s">
         <v>14</v>
@@ -7004,30 +9029,30 @@
     </row>
     <row r="22" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="23" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B23" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C23" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D23" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E23" t="s">
         <v>4</v>
@@ -7159,19 +9184,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>287</v>
+      </c>
+      <c r="B24" t="s">
+        <v>312</v>
+      </c>
+      <c r="C24" t="s">
+        <v>313</v>
+      </c>
+      <c r="D24" t="s">
         <v>289</v>
       </c>
-      <c r="B24" t="s">
-        <v>322</v>
-      </c>
-      <c r="C24" t="s">
-        <v>323</v>
-      </c>
-      <c r="D24" t="s">
-        <v>291</v>
-      </c>
       <c r="E24" t="s">
         <v>2</v>
       </c>
@@ -7302,18 +9327,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B25" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C25" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D25" t="s">
-        <v>325</v>
+        <v>426</v>
       </c>
       <c r="E25" t="s">
         <v>4</v>
@@ -7445,18 +9470,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C26" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D26" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="E26" t="s">
         <v>4</v>
@@ -7588,18 +9613,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C27" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D27" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -7731,18 +9756,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C28" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D28" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="E28" t="s">
         <v>14</v>
@@ -7874,18 +9899,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C29" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D29" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="E29" t="s">
         <v>14</v>
@@ -8017,18 +10042,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C30" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D30" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="E30" t="s">
         <v>14</v>
@@ -8160,18 +10185,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C31" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D31" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="E31" t="s">
         <v>4</v>
@@ -8303,18 +10328,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D32" t="s">
         <v>322</v>
-      </c>
-      <c r="C32" t="s">
-        <v>323</v>
-      </c>
-      <c r="D32" t="s">
-        <v>332</v>
       </c>
       <c r="E32" t="s">
         <v>2</v>
@@ -8446,18 +10471,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C33" t="s">
+        <v>313</v>
+      </c>
+      <c r="D33" t="s">
         <v>323</v>
-      </c>
-      <c r="D33" t="s">
-        <v>333</v>
       </c>
       <c r="E33" t="s">
         <v>4</v>
@@ -8589,18 +10614,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C34" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D34" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="E34" t="s">
         <v>14</v>
@@ -8732,18 +10757,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C35" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D35" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="E35" t="s">
         <v>4</v>
@@ -8875,18 +10900,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:47" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C36" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="D36" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="E36" t="s">
         <v>12</v>
@@ -9171,7 +11196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64E17DB-97BC-41CA-BE02-8ED430425589}">
   <dimension ref="A1:BK48"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -9180,7 +11205,8 @@
     <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="12.140625" bestFit="1" customWidth="1"/>
@@ -9392,7 +11418,7 @@
         <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>337</v>
       </c>
       <c r="C2" t="s">
         <v>97</v>
@@ -10162,7 +12188,7 @@
         <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>397</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -10353,7 +12379,7 @@
         <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
         <v>86</v>
@@ -10544,7 +12570,7 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>86</v>
@@ -10735,7 +12761,7 @@
         <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>86</v>
@@ -10923,10 +12949,10 @@
         <v>96</v>
       </c>
       <c r="C10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" t="s">
         <v>107</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
       </c>
       <c r="E10" t="s">
         <v>86</v>
@@ -11114,10 +13140,10 @@
         <v>96</v>
       </c>
       <c r="C11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" t="s">
         <v>109</v>
-      </c>
-      <c r="D11" t="s">
-        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>86</v>
@@ -11305,10 +13331,10 @@
         <v>96</v>
       </c>
       <c r="C12" t="s">
+        <v>341</v>
+      </c>
+      <c r="D12" t="s">
         <v>111</v>
-      </c>
-      <c r="D12" t="s">
-        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>86</v>
@@ -11496,10 +13522,10 @@
         <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>86</v>
@@ -11687,10 +13713,10 @@
         <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>86</v>
@@ -11878,10 +13904,10 @@
         <v>96</v>
       </c>
       <c r="C15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" t="s">
         <v>115</v>
-      </c>
-      <c r="D15" t="s">
-        <v>116</v>
       </c>
       <c r="E15" t="s">
         <v>86</v>
@@ -12069,10 +14095,10 @@
         <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>388</v>
       </c>
       <c r="E16" t="s">
         <v>86</v>
@@ -12087,7 +14113,7 @@
         <v>8</v>
       </c>
       <c r="I16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J16" t="s">
         <v>10</v>
@@ -12260,10 +14286,10 @@
         <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>390</v>
       </c>
       <c r="E17" t="s">
         <v>86</v>
@@ -12451,10 +14477,10 @@
         <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>392</v>
       </c>
       <c r="E18" t="s">
         <v>86</v>
@@ -12642,10 +14668,10 @@
         <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>393</v>
       </c>
       <c r="E19" t="s">
         <v>86</v>
@@ -12830,13 +14856,13 @@
         <v>95</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -12906,10 +14932,10 @@
         <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>342</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
         <v>86</v>
@@ -13097,10 +15123,10 @@
         <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
         <v>86</v>
@@ -13288,10 +15314,10 @@
         <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
         <v>86</v>
@@ -13479,10 +15505,10 @@
         <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
         <v>86</v>
@@ -13667,13 +15693,13 @@
         <v>99</v>
       </c>
       <c r="B25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" t="s">
         <v>130</v>
-      </c>
-      <c r="C25" t="s">
-        <v>131</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
       </c>
       <c r="E25" t="s">
         <v>86</v>
@@ -13858,13 +15884,13 @@
         <v>99</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>2</v>
@@ -14049,13 +16075,13 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" t="s">
         <v>134</v>
-      </c>
-      <c r="D27" t="s">
-        <v>136</v>
       </c>
       <c r="E27" t="s">
         <v>86</v>
@@ -14240,13 +16266,13 @@
         <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E28" t="s">
         <v>2</v>
@@ -14431,13 +16457,13 @@
         <v>99</v>
       </c>
       <c r="B29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
         <v>86</v>
@@ -14622,13 +16648,13 @@
         <v>99</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>86</v>
@@ -14813,16 +16839,16 @@
         <v>99</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AN31" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -14830,13 +16856,13 @@
         <v>99</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -14903,13 +16929,13 @@
         <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E33" t="s">
         <v>86</v>
@@ -15094,13 +17120,13 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" t="s">
         <v>143</v>
-      </c>
-      <c r="C34" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" t="s">
-        <v>145</v>
       </c>
       <c r="E34" t="s">
         <v>2</v>
@@ -15285,13 +17311,13 @@
         <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E35" t="s">
         <v>4</v>
@@ -15476,13 +17502,13 @@
         <v>99</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -15549,13 +17575,13 @@
         <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E37" t="s">
         <v>86</v>
@@ -15740,13 +17766,13 @@
         <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D38" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E38" t="s">
         <v>86</v>
@@ -15931,13 +17957,13 @@
         <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s">
         <v>2</v>
@@ -16122,13 +18148,13 @@
         <v>99</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
@@ -16195,13 +18221,13 @@
         <v>99</v>
       </c>
       <c r="B41" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E41" t="s">
         <v>86</v>
@@ -16386,13 +18412,13 @@
         <v>99</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D42" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E42" t="s">
         <v>86</v>
@@ -16577,13 +18603,13 @@
         <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E43" t="s">
         <v>86</v>
@@ -16768,13 +18794,13 @@
         <v>99</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>86</v>
@@ -16959,13 +18985,13 @@
         <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D45" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E45" t="s">
         <v>86</v>
@@ -17150,13 +19176,13 @@
         <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D46" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E46" t="s">
         <v>86</v>
@@ -17341,13 +19367,13 @@
         <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C47" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D47" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E47" t="s">
         <v>86</v>
@@ -17532,13 +19558,13 @@
         <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D48" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E48" t="s">
         <v>86</v>
@@ -17727,7 +19753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF086EBD-9A96-4A9C-BD12-3704DB0D29F8}">
   <dimension ref="A1:AG32"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17744,13 +19770,13 @@
   <sheetData>
     <row r="1" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
       <c r="D1" s="63"/>
       <c r="E1" s="54" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F1" s="55"/>
       <c r="G1" s="55"/>
@@ -17773,7 +19799,7 @@
       <c r="X1" s="55"/>
       <c r="Y1" s="56"/>
       <c r="Z1" s="59" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AA1" s="27"/>
     </row>
@@ -17782,37 +19808,37 @@
         <v>17</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D2" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>44</v>
@@ -17821,7 +19847,7 @@
         <v>45</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="P2" s="10" t="s">
         <v>47</v>
@@ -17833,19 +19859,19 @@
         <v>49</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T2" s="10" t="s">
         <v>51</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="V2" s="10" t="s">
         <v>53</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="X2" s="10" t="s">
         <v>55</v>
@@ -17856,36 +19882,36 @@
       <c r="Z2" s="60"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="AD2" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AE2" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AF2" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AG2" s="8" t="s">
         <v>201</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="AG2" s="8" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>117</v>
+        <v>340</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="7"/>
@@ -17913,16 +19939,16 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="47" t="s">
-        <v>118</v>
-      </c>
       <c r="D4" s="39" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="7"/>
@@ -17950,16 +19976,16 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="7"/>
@@ -17987,16 +20013,16 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="7"/>
@@ -18024,16 +20050,16 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="7"/>
@@ -18061,16 +20087,16 @@
     </row>
     <row r="8" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="7"/>
@@ -18090,7 +20116,7 @@
       <c r="T8" s="7"/>
       <c r="U8" s="21"/>
       <c r="V8" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
@@ -18100,16 +20126,16 @@
     </row>
     <row r="9" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="7"/>
@@ -18129,7 +20155,7 @@
       <c r="T9" s="7"/>
       <c r="U9" s="21"/>
       <c r="V9" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -18139,16 +20165,16 @@
     </row>
     <row r="10" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="7"/>
@@ -18167,7 +20193,7 @@
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
       <c r="U10" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V10" s="7"/>
       <c r="W10" s="7"/>
@@ -18178,16 +20204,16 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="47" t="s">
-        <v>112</v>
-      </c>
       <c r="D11" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="7"/>
@@ -18207,7 +20233,7 @@
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -18217,16 +20243,16 @@
     </row>
     <row r="12" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="7"/>
@@ -18245,7 +20271,7 @@
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
       <c r="U12" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V12" s="7"/>
       <c r="W12" s="7"/>
@@ -18256,16 +20282,16 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="50" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="7"/>
@@ -18293,85 +20319,85 @@
     </row>
     <row r="14" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="7"/>
       <c r="G14" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
       <c r="O14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P14" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q14" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="S14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="T14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X14" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y14" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z14" s="35"/>
       <c r="AA14" s="29"/>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="7"/>
@@ -18399,16 +20425,16 @@
     </row>
     <row r="16" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="7"/>
@@ -18416,62 +20442,62 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K16" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L16" s="43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M16" s="7"/>
       <c r="N16" s="43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O16" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P16" s="43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
       <c r="S16" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="T16" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U16" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V16" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W16" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X16" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y16" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z16" s="35"/>
       <c r="AA16" s="29"/>
     </row>
     <row r="17" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="7"/>
@@ -18493,111 +20519,111 @@
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y17" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z17" s="35"/>
       <c r="AA17" s="29"/>
     </row>
     <row r="18" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="E18" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="D18" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="E18" s="41" t="s">
-        <v>218</v>
-      </c>
       <c r="F18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="U18" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="V18" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="W18" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X18" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y18" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z18" s="34"/>
       <c r="AA18" s="8"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D19" s="39" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
@@ -18615,7 +20641,7 @@
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Y19" s="7"/>
       <c r="Z19" s="36"/>
@@ -18623,93 +20649,93 @@
     </row>
     <row r="20" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K20" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O20" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R20" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="S20" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="T20" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U20" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V20" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W20" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X20" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y20" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z20" s="35"/>
       <c r="AA20" s="29"/>
     </row>
     <row r="21" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="7"/>
@@ -18722,53 +20748,53 @@
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
       <c r="O21" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
       <c r="S21" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="T21" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U21" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V21" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W21" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X21" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y21" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z21" s="35"/>
       <c r="AA21" s="29"/>
     </row>
     <row r="22" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
@@ -18777,7 +20803,7 @@
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
@@ -18785,77 +20811,77 @@
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V22" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W22" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X22" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y22" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z22" s="35"/>
       <c r="AA22" s="29"/>
     </row>
     <row r="23" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D23" s="39" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
       <c r="P23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V23" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
@@ -18865,33 +20891,33 @@
     </row>
     <row r="24" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N24" s="7"/>
       <c r="O24" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
@@ -18899,112 +20925,112 @@
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
       <c r="U24" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V24" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W24" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X24" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y24" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z24" s="35"/>
       <c r="AA24" s="29"/>
     </row>
     <row r="25" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Q25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="S25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="T25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y25" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z25" s="35"/>
       <c r="AA25" s="29"/>
     </row>
     <row r="26" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E26" s="44"/>
       <c r="F26" s="44"/>
@@ -19012,56 +21038,56 @@
       <c r="H26" s="44"/>
       <c r="I26" s="44"/>
       <c r="J26" s="43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K26" s="43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L26" s="44"/>
       <c r="M26" s="7"/>
       <c r="N26" s="44"/>
       <c r="O26" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P26" s="44"/>
       <c r="Q26" s="44"/>
       <c r="R26" s="44"/>
       <c r="S26" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="T26" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U26" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V26" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W26" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X26" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y26" s="22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z26" s="35"/>
       <c r="AA26" s="29"/>
     </row>
     <row r="27" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="7"/>
@@ -19079,16 +21105,16 @@
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U27" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V27" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W27" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X27" s="7"/>
       <c r="Y27" s="13"/>
@@ -19097,31 +21123,31 @@
     </row>
     <row r="28" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="49" t="s">
         <v>226</v>
       </c>
-      <c r="B28" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>228</v>
-      </c>
       <c r="D28" s="40" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G28" s="31" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I28" s="32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
@@ -19133,32 +21159,32 @@
       <c r="Q28" s="15"/>
       <c r="R28" s="15"/>
       <c r="S28" s="32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="T28" s="32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="U28" s="32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V28" s="32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="W28" s="32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="X28" s="32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y28" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z28" s="37"/>
       <c r="AA28" s="29"/>
     </row>
     <row r="29" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="57" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B29" s="58"/>
       <c r="C29" s="58"/>
@@ -19231,12 +21257,12 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E31" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E32" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -19253,7 +21279,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F2FAC0-FFC6-48CD-A073-C4F1C5B33885}">
   <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19273,10 +21299,10 @@
         <v>17</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -19284,13 +21310,13 @@
         <v>99</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -19298,13 +21324,13 @@
         <v>99</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -19312,13 +21338,13 @@
         <v>99</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -19326,13 +21352,13 @@
         <v>99</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -19340,13 +21366,13 @@
         <v>99</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -19354,13 +21380,13 @@
         <v>99</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -19368,13 +21394,13 @@
         <v>99</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>123</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -19382,13 +21408,13 @@
         <v>99</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -19396,27 +21422,27 @@
         <v>99</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>99</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>110</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -19424,13 +21450,13 @@
         <v>99</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -19438,13 +21464,13 @@
         <v>99</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -19452,13 +21478,13 @@
         <v>99</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -19466,13 +21492,13 @@
         <v>99</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -19480,13 +21506,13 @@
         <v>99</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -19494,13 +21520,13 @@
         <v>99</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -19508,13 +21534,13 @@
         <v>99</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -19522,13 +21548,13 @@
         <v>99</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>180</v>
+        <v>355</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -19536,13 +21562,13 @@
         <v>99</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -19550,13 +21576,13 @@
         <v>99</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -19564,13 +21590,13 @@
         <v>99</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -19578,13 +21604,13 @@
         <v>99</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -19592,13 +21618,13 @@
         <v>99</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -19606,13 +21632,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -19620,13 +21646,13 @@
         <v>99</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -19634,13 +21660,13 @@
         <v>99</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -19648,13 +21674,13 @@
         <v>99</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/TC Finishing D^t Solution Migration_2026.xlsx
+++ b/TC Finishing D^t Solution Migration_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corningonline-my.sharepoint.com/personal/wangm44_corning_com/Documents/桌面/Project/Dt_Quality_Roadmap/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangm44\Project\Dt_Quality_Roadmap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="515" documentId="14_{89C73AE1-523B-4B10-8D61-849337C2FCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1BB2A86-7869-4B1B-95BD-A204095BBA20}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0546802D-6A1B-44CD-8B46-512262E44C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Definition" sheetId="6" r:id="rId1"/>
@@ -963,9 +963,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Tilter/SA TAM sensor</t>
-  </si>
-  <si>
     <t>N/A</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -1897,6 +1894,10 @@
   </si>
   <si>
     <t>BKG detection system; Wet zone glass BKG detective system; Cell grinder BKG detection system at OUT C/V</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAM sensor</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2640,6 +2641,7 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2670,7 +2672,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3599,7 +3600,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>13</v>
@@ -3632,182 +3633,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="64" t="s">
-        <v>329</v>
-      </c>
-      <c r="C1" s="64" t="s">
+      <c r="B1" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="E1" s="64" t="s">
-        <v>440</v>
-      </c>
-      <c r="F1" s="64" t="s">
-        <v>406</v>
+      <c r="E1" s="54" t="s">
+        <v>439</v>
+      </c>
+      <c r="F1" s="54" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D3" t="s">
         <v>313</v>
       </c>
-      <c r="D3" t="s">
-        <v>314</v>
-      </c>
       <c r="E3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E10" t="s">
         <v>205</v>
@@ -3815,397 +3816,397 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F11" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E12" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C14" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E14" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B15" t="s">
+        <v>332</v>
+      </c>
+      <c r="C15" t="s">
         <v>333</v>
       </c>
-      <c r="C15" t="s">
-        <v>334</v>
-      </c>
       <c r="D15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B16" t="s">
+        <v>332</v>
+      </c>
+      <c r="C16" t="s">
         <v>333</v>
       </c>
-      <c r="C16" t="s">
-        <v>334</v>
-      </c>
       <c r="D16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E16" t="s">
         <v>445</v>
       </c>
-      <c r="E16" t="s">
-        <v>446</v>
-      </c>
       <c r="F16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B17" t="s">
+        <v>332</v>
+      </c>
+      <c r="C17" t="s">
         <v>333</v>
       </c>
-      <c r="C17" t="s">
-        <v>334</v>
-      </c>
       <c r="D17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B18" t="s">
+        <v>332</v>
+      </c>
+      <c r="C18" t="s">
         <v>333</v>
       </c>
-      <c r="C18" t="s">
-        <v>334</v>
-      </c>
       <c r="D18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B19" t="s">
+        <v>332</v>
+      </c>
+      <c r="C19" t="s">
         <v>333</v>
       </c>
-      <c r="C19" t="s">
-        <v>334</v>
-      </c>
       <c r="D19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E19" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B20" t="s">
+        <v>332</v>
+      </c>
+      <c r="C20" t="s">
         <v>333</v>
       </c>
-      <c r="C20" t="s">
-        <v>334</v>
-      </c>
       <c r="D20" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E21" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B22" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E22" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C23" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E23" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C24" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F24" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C25" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E25" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F25" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D26" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E26" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E27" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C28" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E28" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D29" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F29" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D30" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E30" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C31" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D31" t="s">
         <v>187</v>
       </c>
       <c r="E31" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C32" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E32" t="s">
         <v>205</v>
@@ -4216,7 +4217,7 @@
         <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C33" t="s">
         <v>164</v>
@@ -4233,19 +4234,19 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C34" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D34" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E34" t="s">
         <v>205</v>
       </c>
       <c r="F34" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4253,13 +4254,13 @@
         <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C35" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D35" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4267,13 +4268,13 @@
         <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D36" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4281,16 +4282,16 @@
         <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C37" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D37" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E37" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4298,16 +4299,16 @@
         <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C38" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D38" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E38" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4315,16 +4316,16 @@
         <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C39" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D39" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E39" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4332,16 +4333,16 @@
         <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D40" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E40" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4349,13 +4350,13 @@
         <v>99</v>
       </c>
       <c r="B41" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D41" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E41" t="s">
         <v>205</v>
@@ -4366,13 +4367,13 @@
         <v>99</v>
       </c>
       <c r="B42" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C42" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D42" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E42" t="s">
         <v>205</v>
@@ -4383,10 +4384,10 @@
         <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4394,10 +4395,10 @@
         <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C44" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4405,19 +4406,19 @@
         <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C45" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D45" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E45" t="s">
         <v>205</v>
       </c>
       <c r="F45" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4425,19 +4426,19 @@
         <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C46" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D46" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E46" t="s">
         <v>219</v>
       </c>
       <c r="F46" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4445,13 +4446,13 @@
         <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C47" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D47" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4459,16 +4460,16 @@
         <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C48" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D48" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E48" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4476,19 +4477,19 @@
         <v>99</v>
       </c>
       <c r="B49" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C49" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D49" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E49" t="s">
         <v>219</v>
       </c>
       <c r="F49" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4496,10 +4497,10 @@
         <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C50" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4507,10 +4508,10 @@
         <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C51" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4518,10 +4519,10 @@
         <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4529,10 +4530,10 @@
         <v>99</v>
       </c>
       <c r="B53" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C53" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4540,10 +4541,10 @@
         <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C54" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4551,19 +4552,19 @@
         <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C55" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D55" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E55" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F55" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4571,16 +4572,16 @@
         <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C56" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D56" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E56" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4588,16 +4589,16 @@
         <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C57" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D57" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E57" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4605,16 +4606,16 @@
         <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C58" t="s">
         <v>176</v>
       </c>
       <c r="D58" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E58" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4622,7 +4623,7 @@
         <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C59" t="s">
         <v>178</v>
@@ -4631,7 +4632,7 @@
         <v>175</v>
       </c>
       <c r="E59" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4639,16 +4640,16 @@
         <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C60" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D60" t="s">
         <v>179</v>
       </c>
       <c r="E60" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4656,10 +4657,10 @@
         <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C61" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4667,16 +4668,16 @@
         <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C62" t="s">
         <v>181</v>
       </c>
       <c r="D62" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E62" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4684,10 +4685,10 @@
         <v>99</v>
       </c>
       <c r="B63" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C63" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4695,16 +4696,16 @@
         <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C64" t="s">
+        <v>419</v>
+      </c>
+      <c r="D64" t="s">
         <v>420</v>
       </c>
-      <c r="D64" t="s">
-        <v>421</v>
-      </c>
       <c r="E64" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4721,7 +4722,7 @@
         <v>182</v>
       </c>
       <c r="E65" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4735,13 +4736,13 @@
         <v>183</v>
       </c>
       <c r="D66" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E66" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F66" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4752,16 +4753,16 @@
         <v>180</v>
       </c>
       <c r="C67" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D67" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E67" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F67" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4772,10 +4773,10 @@
         <v>180</v>
       </c>
       <c r="C68" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D68" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E68" t="s">
         <v>205</v>
@@ -4792,13 +4793,13 @@
         <v>185</v>
       </c>
       <c r="D69" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E69" t="s">
         <v>205</v>
       </c>
       <c r="F69" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4815,7 +4816,7 @@
         <v>187</v>
       </c>
       <c r="E70" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4829,13 +4830,13 @@
         <v>185</v>
       </c>
       <c r="D71" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E71" t="s">
         <v>205</v>
       </c>
       <c r="F71" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -4849,13 +4850,13 @@
         <v>185</v>
       </c>
       <c r="D72" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E72" t="s">
         <v>205</v>
       </c>
       <c r="F72" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4872,7 +4873,7 @@
         <v>189</v>
       </c>
       <c r="E73" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4886,10 +4887,10 @@
         <v>185</v>
       </c>
       <c r="D74" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E74" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4900,16 +4901,16 @@
         <v>180</v>
       </c>
       <c r="C75" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D75" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E75" t="s">
         <v>205</v>
       </c>
       <c r="F75" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4920,135 +4921,135 @@
         <v>180</v>
       </c>
       <c r="C76" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D76" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E76" t="s">
         <v>205</v>
       </c>
       <c r="F76" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B77" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C77" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D77" t="s">
         <v>226</v>
       </c>
       <c r="E77" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B78" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C78" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D78" t="s">
         <v>85</v>
       </c>
       <c r="E78" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B79" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C79" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D79" t="s">
         <v>87</v>
       </c>
       <c r="E79" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B80" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C80" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D80" t="s">
         <v>88</v>
       </c>
       <c r="E80" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B81" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C81" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D81" t="s">
         <v>89</v>
       </c>
       <c r="E81" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B82" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C82" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D82" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E82" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B83" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C83" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D83" t="s">
         <v>171</v>
       </c>
       <c r="E83" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -6287,10 +6288,10 @@
         <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D1" t="s">
         <v>19</v>
@@ -6302,141 +6303,141 @@
         <v>80</v>
       </c>
       <c r="G1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H1" t="s">
         <v>249</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>250</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>251</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>252</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>253</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>254</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>255</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>256</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>257</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>258</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>259</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>260</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>261</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>262</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>263</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>264</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>265</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>266</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>267</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>268</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>269</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>270</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>271</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>272</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>273</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>274</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>275</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>276</v>
       </c>
       <c r="AI1" t="s">
         <v>81</v>
       </c>
       <c r="AJ1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AK1" t="s">
         <v>82</v>
       </c>
       <c r="AL1" t="s">
+        <v>277</v>
+      </c>
+      <c r="AM1" t="s">
         <v>278</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>279</v>
       </c>
       <c r="AN1" t="s">
         <v>83</v>
       </c>
       <c r="AO1" t="s">
+        <v>279</v>
+      </c>
+      <c r="AP1" t="s">
         <v>280</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>281</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>282</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>283</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>284</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>285</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" t="s">
         <v>287</v>
       </c>
-      <c r="B2" t="s">
-        <v>288</v>
-      </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
@@ -6570,16 +6571,16 @@
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6713,16 +6714,16 @@
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" t="s">
         <v>287</v>
       </c>
-      <c r="B4" t="s">
-        <v>288</v>
-      </c>
       <c r="C4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
@@ -6856,16 +6857,16 @@
     </row>
     <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" t="s">
         <v>287</v>
       </c>
-      <c r="B5" t="s">
-        <v>288</v>
-      </c>
       <c r="C5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -6999,16 +7000,16 @@
     </row>
     <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B6" t="s">
         <v>287</v>
       </c>
-      <c r="B6" t="s">
-        <v>288</v>
-      </c>
       <c r="C6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -7142,16 +7143,16 @@
     </row>
     <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B7" t="s">
         <v>287</v>
       </c>
-      <c r="B7" t="s">
-        <v>288</v>
-      </c>
       <c r="C7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -7285,16 +7286,16 @@
     </row>
     <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" t="s">
         <v>287</v>
       </c>
-      <c r="B8" t="s">
-        <v>288</v>
-      </c>
       <c r="C8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E8" t="s">
         <v>4</v>
@@ -7428,30 +7429,30 @@
     </row>
     <row r="9" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B10" t="s">
         <v>287</v>
       </c>
-      <c r="B10" t="s">
-        <v>288</v>
-      </c>
       <c r="C10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E10" t="s">
         <v>2</v>
@@ -7585,16 +7586,16 @@
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" t="s">
         <v>287</v>
       </c>
-      <c r="B11" t="s">
-        <v>288</v>
-      </c>
       <c r="C11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -7728,16 +7729,16 @@
     </row>
     <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B12" t="s">
         <v>287</v>
       </c>
-      <c r="B12" t="s">
-        <v>288</v>
-      </c>
       <c r="C12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D12" t="s">
         <v>299</v>
-      </c>
-      <c r="D12" t="s">
-        <v>300</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -7871,30 +7872,30 @@
     </row>
     <row r="13" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" t="s">
         <v>287</v>
       </c>
-      <c r="B14" t="s">
-        <v>288</v>
-      </c>
       <c r="C14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D14" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E14" t="s">
         <v>2</v>
@@ -8028,16 +8029,16 @@
     </row>
     <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>286</v>
+      </c>
+      <c r="B15" t="s">
         <v>287</v>
       </c>
-      <c r="B15" t="s">
-        <v>288</v>
-      </c>
       <c r="C15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D15" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -8171,16 +8172,16 @@
     </row>
     <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>286</v>
+      </c>
+      <c r="B16" t="s">
         <v>287</v>
       </c>
-      <c r="B16" t="s">
-        <v>288</v>
-      </c>
       <c r="C16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E16" t="s">
         <v>2</v>
@@ -8314,16 +8315,16 @@
     </row>
     <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>286</v>
+      </c>
+      <c r="B17" t="s">
         <v>287</v>
       </c>
-      <c r="B17" t="s">
-        <v>288</v>
-      </c>
       <c r="C17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E17" t="s">
         <v>2</v>
@@ -8457,16 +8458,16 @@
     </row>
     <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>286</v>
+      </c>
+      <c r="B18" t="s">
         <v>287</v>
       </c>
-      <c r="B18" t="s">
-        <v>288</v>
-      </c>
       <c r="C18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -8600,16 +8601,16 @@
     </row>
     <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>286</v>
+      </c>
+      <c r="B19" t="s">
         <v>287</v>
       </c>
-      <c r="B19" t="s">
-        <v>288</v>
-      </c>
       <c r="C19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E19" t="s">
         <v>14</v>
@@ -8743,16 +8744,16 @@
     </row>
     <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>286</v>
+      </c>
+      <c r="B20" t="s">
         <v>287</v>
       </c>
-      <c r="B20" t="s">
-        <v>288</v>
-      </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E20" t="s">
         <v>2</v>
@@ -8886,16 +8887,16 @@
     </row>
     <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>286</v>
+      </c>
+      <c r="B21" t="s">
         <v>287</v>
       </c>
-      <c r="B21" t="s">
-        <v>288</v>
-      </c>
       <c r="C21" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E21" t="s">
         <v>14</v>
@@ -9029,30 +9030,30 @@
     </row>
     <row r="22" spans="1:47" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E23" t="s">
         <v>4</v>
@@ -9186,16 +9187,16 @@
     </row>
     <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B24" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24" t="s">
         <v>312</v>
       </c>
-      <c r="C24" t="s">
-        <v>313</v>
-      </c>
       <c r="D24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E24" t="s">
         <v>2</v>
@@ -9329,16 +9330,16 @@
     </row>
     <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s">
+        <v>311</v>
+      </c>
+      <c r="C25" t="s">
         <v>312</v>
       </c>
-      <c r="C25" t="s">
-        <v>313</v>
-      </c>
       <c r="D25" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E25" t="s">
         <v>4</v>
@@ -9472,16 +9473,16 @@
     </row>
     <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s">
+        <v>311</v>
+      </c>
+      <c r="C26" t="s">
         <v>312</v>
       </c>
-      <c r="C26" t="s">
-        <v>313</v>
-      </c>
       <c r="D26" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E26" t="s">
         <v>4</v>
@@ -9615,16 +9616,16 @@
     </row>
     <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s">
+        <v>311</v>
+      </c>
+      <c r="C27" t="s">
         <v>312</v>
       </c>
-      <c r="C27" t="s">
-        <v>313</v>
-      </c>
       <c r="D27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -9758,16 +9759,16 @@
     </row>
     <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s">
+        <v>311</v>
+      </c>
+      <c r="C28" t="s">
         <v>312</v>
       </c>
-      <c r="C28" t="s">
-        <v>313</v>
-      </c>
       <c r="D28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E28" t="s">
         <v>14</v>
@@ -9901,16 +9902,16 @@
     </row>
     <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s">
+        <v>311</v>
+      </c>
+      <c r="C29" t="s">
         <v>312</v>
       </c>
-      <c r="C29" t="s">
-        <v>313</v>
-      </c>
       <c r="D29" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E29" t="s">
         <v>14</v>
@@ -10044,16 +10045,16 @@
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s">
+        <v>311</v>
+      </c>
+      <c r="C30" t="s">
         <v>312</v>
       </c>
-      <c r="C30" t="s">
-        <v>313</v>
-      </c>
       <c r="D30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E30" t="s">
         <v>14</v>
@@ -10187,16 +10188,16 @@
     </row>
     <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s">
+        <v>311</v>
+      </c>
+      <c r="C31" t="s">
         <v>312</v>
       </c>
-      <c r="C31" t="s">
-        <v>313</v>
-      </c>
       <c r="D31" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E31" t="s">
         <v>4</v>
@@ -10330,16 +10331,16 @@
     </row>
     <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s">
+        <v>311</v>
+      </c>
+      <c r="C32" t="s">
         <v>312</v>
       </c>
-      <c r="C32" t="s">
-        <v>313</v>
-      </c>
       <c r="D32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E32" t="s">
         <v>2</v>
@@ -10473,16 +10474,16 @@
     </row>
     <row r="33" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s">
+        <v>311</v>
+      </c>
+      <c r="C33" t="s">
         <v>312</v>
       </c>
-      <c r="C33" t="s">
-        <v>313</v>
-      </c>
       <c r="D33" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E33" t="s">
         <v>4</v>
@@ -10616,16 +10617,16 @@
     </row>
     <row r="34" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s">
+        <v>311</v>
+      </c>
+      <c r="C34" t="s">
         <v>312</v>
       </c>
-      <c r="C34" t="s">
-        <v>313</v>
-      </c>
       <c r="D34" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E34" t="s">
         <v>14</v>
@@ -10759,16 +10760,16 @@
     </row>
     <row r="35" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C35" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D35" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E35" t="s">
         <v>4</v>
@@ -10902,16 +10903,16 @@
     </row>
     <row r="36" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C36" t="s">
+        <v>324</v>
+      </c>
+      <c r="D36" t="s">
         <v>325</v>
-      </c>
-      <c r="D36" t="s">
-        <v>326</v>
       </c>
       <c r="E36" t="s">
         <v>12</v>
@@ -11418,7 +11419,7 @@
         <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
         <v>97</v>
@@ -12188,7 +12189,7 @@
         <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E6" t="s">
         <v>86</v>
@@ -13331,7 +13332,7 @@
         <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D12" t="s">
         <v>111</v>
@@ -14098,7 +14099,7 @@
         <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E16" t="s">
         <v>86</v>
@@ -14113,7 +14114,7 @@
         <v>8</v>
       </c>
       <c r="I16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J16" t="s">
         <v>10</v>
@@ -14289,7 +14290,7 @@
         <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E17" t="s">
         <v>86</v>
@@ -14480,7 +14481,7 @@
         <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E18" t="s">
         <v>86</v>
@@ -14671,7 +14672,7 @@
         <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E19" t="s">
         <v>86</v>
@@ -14932,7 +14933,7 @@
         <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D21" t="s">
         <v>123</v>
@@ -19769,36 +19770,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="54" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="55" t="s">
         <v>193</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="59" t="s">
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="60" t="s">
         <v>194</v>
       </c>
       <c r="AA1" s="27"/>
@@ -19817,28 +19818,28 @@
         <v>195</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>239</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>44</v>
@@ -19847,7 +19848,7 @@
         <v>45</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P2" s="10" t="s">
         <v>47</v>
@@ -19859,19 +19860,19 @@
         <v>49</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="T2" s="10" t="s">
         <v>51</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V2" s="10" t="s">
         <v>53</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="X2" s="10" t="s">
         <v>55</v>
@@ -19879,7 +19880,7 @@
       <c r="Y2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="Z2" s="60"/>
+      <c r="Z2" s="61"/>
       <c r="AA2" s="28"/>
       <c r="AB2" s="8" t="s">
         <v>196</v>
@@ -19905,7 +19906,7 @@
         <v>163</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C3" s="47" t="s">
         <v>168</v>
@@ -20428,10 +20429,10 @@
         <v>132</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>174</v>
+        <v>400</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>228</v>
+        <v>481</v>
       </c>
       <c r="D16" s="39" t="s">
         <v>211</v>
@@ -20544,49 +20545,49 @@
         <v>216</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>209</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I18" s="20" t="s">
         <v>209</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="U18" s="20" t="s">
         <v>209</v>
@@ -20658,7 +20659,7 @@
         <v>157</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E20" s="42" t="s">
         <v>208</v>
@@ -20735,7 +20736,7 @@
         <v>157</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="7"/>
@@ -20953,7 +20954,7 @@
         <v>189</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E25" s="18" t="s">
         <v>208</v>
@@ -21030,7 +21031,7 @@
         <v>157</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E26" s="44"/>
       <c r="F26" s="44"/>
@@ -21087,7 +21088,7 @@
         <v>157</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="7"/>
@@ -21132,7 +21133,7 @@
         <v>226</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>209</v>
@@ -21183,11 +21184,11 @@
       <c r="AA28" s="29"/>
     </row>
     <row r="29" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="58" t="s">
         <v>227</v>
       </c>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
       <c r="D29" s="23"/>
       <c r="E29" s="24">
         <v>3</v>
@@ -21257,12 +21258,12 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E31" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E32" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -21400,7 +21401,7 @@
         <v>116</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -21431,7 +21432,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>99</v>
       </c>
@@ -21442,7 +21443,7 @@
         <v>110</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -21551,7 +21552,7 @@
         <v>132</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>179</v>
